--- a/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/ValueSet-tiflow-chargeitem-operation-outcome-details-vs.xlsx
+++ b/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/ValueSet-tiflow-chargeitem-operation-outcome-details-vs.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -119,61 +119,118 @@
     <t>TIFLOW_AUTH_ROLE_NOT_ALLOWED</t>
   </si>
   <si>
+    <t>Access role not allowed</t>
+  </si>
+  <si>
     <t>TIFLOW_CONSENT_ALREADY_EXISTS</t>
   </si>
   <si>
+    <t>Consent already exists</t>
+  </si>
+  <si>
     <t>TIFLOW_CONSENT_CATEGORY_REQUIRED</t>
   </si>
   <si>
+    <t>Consent category required</t>
+  </si>
+  <si>
     <t>TIFLOW_CONSENT_CATEGORY_INVALID</t>
   </si>
   <si>
+    <t>Consent category invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_ACCESSCODE_MISMATCH</t>
   </si>
   <si>
+    <t>Access code mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_REQUIRED</t>
   </si>
   <si>
+    <t>Task required</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_NOT_FOUND</t>
   </si>
   <si>
+    <t>Task not found</t>
+  </si>
+  <si>
     <t>TIFLOW_SECRET_MISMATCH</t>
   </si>
   <si>
+    <t>Task secret mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_CONSENT_REQUIRED</t>
   </si>
   <si>
+    <t>Consent required</t>
+  </si>
+  <si>
     <t>TIFLOW_OCSP_BACKEND_ERROR</t>
   </si>
   <si>
+    <t>Invalid OCSP response</t>
+  </si>
+  <si>
     <t>TIFLOW_MESSAGE_TO_SELF</t>
   </si>
   <si>
+    <t>Message to self not allowed</t>
+  </si>
+  <si>
     <t>TIFLOW_COMMUNICATION_PAYLOAD_INVALID</t>
   </si>
   <si>
+    <t>Communication payload invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_INSURANT_NOT_ELIGIBLE</t>
   </si>
   <si>
+    <t>Insurant not eligible</t>
+  </si>
+  <si>
     <t>TIFLOW_RECIPIENT_INVALID</t>
   </si>
   <si>
+    <t>Recipient invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_STATUS_MISMATCH</t>
   </si>
   <si>
+    <t>Task status mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_EXPIRED</t>
   </si>
   <si>
+    <t>Task expired</t>
+  </si>
+  <si>
     <t>TIFLOW_MVO_NOT_VALID_YET</t>
   </si>
   <si>
+    <t>MVO not valid yet</t>
+  </si>
+  <si>
     <t>https://gematik.de/fhir/tiflow/core/CodeSystem/tiflow-operation-outcome-details-cs</t>
   </si>
   <si>
     <t>SVC_IDENTITY_MISMATCH</t>
   </si>
   <si>
+    <t>Identity mismatch: Access token or x-insurantid header does not match FHIR data (Telematik-ID / KVNR)</t>
+  </si>
+  <si>
     <t>SVC_VALIDATION_FAILED</t>
+  </si>
+  <si>
+    <t>FHIR Profile Validation Failed</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/ti/CodeSystem/operation-outcome-details-codes</t>
@@ -497,103 +554,137 @@
       <c r="A2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B16" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B17" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B18" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -608,7 +699,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -635,15 +726,19 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -658,7 +753,7 @@
         <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
